--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98421440849412</v>
+        <v>1.947434841380295</v>
       </c>
       <c r="D2" t="n">
-        <v>2.241513528769242</v>
+        <v>0.3642459484250019</v>
       </c>
       <c r="E2" t="n">
-        <v>12.55046435013424</v>
+        <v>2.039450456896815</v>
       </c>
       <c r="F2" t="n">
-        <v>14.4467453509761</v>
+        <v>2.347596119533616</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.01397393251003</v>
+        <v>2.60227076403288</v>
       </c>
       <c r="D3" t="n">
-        <v>12.3499637626299</v>
+        <v>2.006869111427358</v>
       </c>
       <c r="E3" t="n">
-        <v>12.55046435013424</v>
+        <v>2.039450456896815</v>
       </c>
       <c r="F3" t="n">
-        <v>14.4467453509761</v>
+        <v>2.347596119533616</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.81262635817647</v>
+        <v>6.957051783203677</v>
       </c>
       <c r="D4" t="n">
-        <v>35.47319063343896</v>
+        <v>5.764393477933831</v>
       </c>
       <c r="E4" t="n">
-        <v>12.55046435013424</v>
+        <v>2.039450456896815</v>
       </c>
       <c r="F4" t="n">
-        <v>14.4467453509761</v>
+        <v>2.347596119533616</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.15747899131913</v>
+        <v>5.388090336089359</v>
       </c>
       <c r="D5" t="n">
-        <v>35.10672378213889</v>
+        <v>5.704842614597569</v>
       </c>
       <c r="E5" t="n">
-        <v>12.55046435013424</v>
+        <v>2.039450456896815</v>
       </c>
       <c r="F5" t="n">
-        <v>14.4467453509761</v>
+        <v>2.347596119533616</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
